--- a/SType1.xlsx
+++ b/SType1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://icrafcifor-my.sharepoint.com/personal/d_bodro_landscapealliance_org/Documents/Documents/GitHub/Regional-Economy-GGP-Sumsel-2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="8_{E14BC35D-6BC9-48AC-B635-C08D3D528CEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1979E371-CC40-4A24-9BEA-53E0621AEED9}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="8_{E14BC35D-6BC9-48AC-B635-C08D3D528CEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{401E96BD-8D0E-47EA-978F-944648654AA2}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{3F3D8CF6-D9DE-4B5B-B053-76B7C1F2A466}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{3F3D8CF6-D9DE-4B5B-B053-76B7C1F2A466}"/>
   </bookViews>
   <sheets>
     <sheet name="SType1" sheetId="1" r:id="rId1"/>
@@ -684,7 +684,7 @@
         <v>0</v>
       </c>
       <c r="E4" s="1">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="F4" s="1">
         <v>0</v>
@@ -850,7 +850,7 @@
         <v>0</v>
       </c>
       <c r="E6" s="1">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="F6" s="1">
         <v>0</v>
@@ -1099,7 +1099,7 @@
         <v>0</v>
       </c>
       <c r="E9" s="1">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="F9" s="1">
         <v>0</v>
@@ -1182,7 +1182,7 @@
         <v>0</v>
       </c>
       <c r="E10" s="1">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="F10">
         <v>0.05</v>

--- a/SType1.xlsx
+++ b/SType1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://icrafcifor-my.sharepoint.com/personal/d_bodro_landscapealliance_org/Documents/Documents/GitHub/Regional-Economy-GGP-Sumsel-2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="8_{E14BC35D-6BC9-48AC-B635-C08D3D528CEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{401E96BD-8D0E-47EA-978F-944648654AA2}"/>
+  <xr:revisionPtr revIDLastSave="5" documentId="8_{E14BC35D-6BC9-48AC-B635-C08D3D528CEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{403A67FE-26F7-4989-B5EC-0BFE10DF4693}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{3F3D8CF6-D9DE-4B5B-B053-76B7C1F2A466}"/>
+    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="13872" xr2:uid="{3F3D8CF6-D9DE-4B5B-B053-76B7C1F2A466}"/>
   </bookViews>
   <sheets>
     <sheet name="SType1" sheetId="1" r:id="rId1"/>
@@ -506,19 +506,19 @@
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A2" s="1">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="B2" s="1">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="C2" s="1">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="D2" s="1">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="E2" s="1">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="F2" s="1">
         <v>0</v>
@@ -530,7 +530,7 @@
         <v>0</v>
       </c>
       <c r="I2">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="J2" s="1">
         <v>0</v>
@@ -589,19 +589,19 @@
     </row>
     <row r="3" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="B3" s="1">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="C3" s="1">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="D3" s="1">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="E3" s="1">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="F3" s="1">
         <v>0</v>
@@ -613,7 +613,7 @@
         <v>0</v>
       </c>
       <c r="I3">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="J3" s="1">
         <v>0</v>
@@ -684,7 +684,7 @@
         <v>0</v>
       </c>
       <c r="E4" s="1">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="F4" s="1">
         <v>0</v>
@@ -838,19 +838,19 @@
     </row>
     <row r="6" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A6">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
       <c r="B6">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
       <c r="C6">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
       <c r="D6" s="1">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="E6" s="1">
-        <v>0.04</v>
+        <v>0.1</v>
       </c>
       <c r="F6" s="1">
         <v>0</v>
@@ -1087,31 +1087,31 @@
     </row>
     <row r="9" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A9">
-        <v>0.05</v>
+        <v>0.2</v>
       </c>
       <c r="B9">
+        <v>0.2</v>
+      </c>
+      <c r="C9">
+        <v>0.2</v>
+      </c>
+      <c r="D9" s="1">
+        <v>0.2</v>
+      </c>
+      <c r="E9" s="1">
+        <v>0.2</v>
+      </c>
+      <c r="F9" s="1">
+        <v>0</v>
+      </c>
+      <c r="G9" s="1">
+        <v>0</v>
+      </c>
+      <c r="H9">
+        <v>1</v>
+      </c>
+      <c r="I9" s="1">
         <v>0.1</v>
-      </c>
-      <c r="C9">
-        <v>0.13</v>
-      </c>
-      <c r="D9" s="1">
-        <v>0</v>
-      </c>
-      <c r="E9" s="1">
-        <v>0.04</v>
-      </c>
-      <c r="F9" s="1">
-        <v>0</v>
-      </c>
-      <c r="G9" s="1">
-        <v>0</v>
-      </c>
-      <c r="H9">
-        <v>0.4</v>
-      </c>
-      <c r="I9" s="1">
-        <v>0</v>
       </c>
       <c r="J9" s="1">
         <v>0</v>
@@ -1182,7 +1182,7 @@
         <v>0</v>
       </c>
       <c r="E10" s="1">
-        <v>0.04</v>
+        <v>0</v>
       </c>
       <c r="F10">
         <v>0.05</v>
@@ -4988,19 +4988,19 @@
     </row>
     <row r="56" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A56">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="B56">
-        <v>0.85</v>
+        <v>0.5</v>
       </c>
       <c r="C56">
-        <v>0.82000000000000006</v>
+        <v>0.5</v>
       </c>
       <c r="D56">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="E56">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F56">
         <v>0.95</v>
@@ -5009,10 +5009,10 @@
         <v>0.91</v>
       </c>
       <c r="H56">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="I56">
-        <v>0.30000000000000004</v>
+        <v>0</v>
       </c>
       <c r="J56">
         <v>0</v>
